--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_166_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_166_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.432700000000001</v>
+        <v>9.475899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7483</v>
+        <v>7.2201</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6844</v>
+        <v>2.2558</v>
       </c>
       <c r="G2" t="n">
         <v>4.3534</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7789</v>
+        <v>0.2642</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4323</v>
+        <v>0.0395</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3466</v>
+        <v>0.2247</v>
       </c>
       <c r="V2" t="n">
         <v>2.5387</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.8662</v>
+        <v>6.5501</v>
       </c>
       <c r="E3" t="n">
-        <v>5.9716</v>
+        <v>4.8264</v>
       </c>
       <c r="F3" t="n">
-        <v>1.8946</v>
+        <v>1.7236</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8297</v>
+        <v>2.2686</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2278</v>
+        <v>2.1716</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3981</v>
+        <v>0.097</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8259</v>
+        <v>2.2652</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6419</v>
+        <v>2.2687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.184</v>
+        <v>-0.0035</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0039</v>
+        <v>0.0035</v>
       </c>
       <c r="N3" t="n">
-        <v>0.586</v>
+        <v>-0.097</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5821</v>
+        <v>0.1005</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0391</v>
+        <v>1.0495</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0039</v>
+        <v>0.4169</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0351</v>
+        <v>0.6326000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.3801</v>
+        <v>6.0969</v>
       </c>
       <c r="E4" t="n">
-        <v>4.1187</v>
+        <v>4.2023</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2613</v>
+        <v>1.8946</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2686</v>
+        <v>2.8297</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1716</v>
+        <v>3.2278</v>
       </c>
       <c r="I4" t="n">
-        <v>0.097</v>
+        <v>-0.3981</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2652</v>
+        <v>2.8259</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2687</v>
+        <v>2.6419</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0035</v>
+        <v>0.184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0035</v>
+        <v>0.0039</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.097</v>
+        <v>0.586</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1005</v>
+        <v>-0.5821</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8794999999999999</v>
+        <v>1.2698</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2908</v>
+        <v>1.2346</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1703</v>
+        <v>0.0351</v>
       </c>
       <c r="V4" t="n">
-        <v>1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1444</v>
+        <v>0.1418</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.8051</v>
+        <v>5.4612</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2051</v>
+        <v>2.2554</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6</v>
+        <v>3.2058</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4103</v>
+        <v>5.9819</v>
       </c>
       <c r="H5" t="n">
-        <v>2.132</v>
+        <v>3.8271</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2783</v>
+        <v>2.1548</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2399</v>
+        <v>4.6991</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1124</v>
+        <v>3.3274</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1275</v>
+        <v>1.3717</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8297</v>
+        <v>1.2828</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9804</v>
+        <v>0.4997</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1507</v>
+        <v>0.7831</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1655</v>
+        <v>0.5669</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9831</v>
+        <v>0.4995</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1823</v>
+        <v>0.0674</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4511</v>
+        <v>5.1652</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5477</v>
+        <v>3.7333</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9034</v>
+        <v>1.4319</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9819</v>
+        <v>3.4103</v>
       </c>
       <c r="H6" t="n">
-        <v>3.8271</v>
+        <v>2.132</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1548</v>
+        <v>1.2783</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6991</v>
+        <v>4.2399</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3274</v>
+        <v>3.1124</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3717</v>
+        <v>1.1275</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2828</v>
+        <v>-0.8297</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4997</v>
+        <v>-0.9804</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7831</v>
+        <v>0.1507</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6237</v>
+        <v>1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4432</v>
+        <v>0.5256</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2082</v>
+        <v>0.5113</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.235</v>
+        <v>0.0143</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>-0.3943</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2258</v>
+        <v>0.7712</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7578</v>
+        <v>0.404</v>
       </c>
       <c r="F7" t="n">
-        <v>0.468</v>
+        <v>0.3672</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0828</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0767</v>
+        <v>0.6221</v>
       </c>
       <c r="T7" t="n">
-        <v>0.637</v>
+        <v>0.2831</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4397</v>
+        <v>0.3389</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Y. MAKOUNDOU</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.803</v>
+        <v>0.673</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1734</v>
+        <v>-0.232</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6296</v>
+        <v>0.905</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3726</v>
+        <v>1.2766</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7407</v>
+        <v>0.2895</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.368</v>
+        <v>0.9871</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3228</v>
+        <v>2.2918</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1091</v>
+        <v>0.7226</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7863</v>
+        <v>1.5692</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0499</v>
+        <v>-1.0152</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3684</v>
+        <v>-0.4331</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4183</v>
+        <v>-0.5821</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.036</v>
+        <v>0.3242</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>-0.2043</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1854</v>
+        <v>0.5285</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>Y. MAKOUNDOU</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6387</v>
+        <v>0.6686</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4679</v>
+        <v>0.1734</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1066</v>
+        <v>0.4951</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2766</v>
+        <v>0.3726</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2895</v>
+        <v>0.7407</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9871</v>
+        <v>-0.368</v>
       </c>
       <c r="J9" t="n">
-        <v>2.2918</v>
+        <v>0.3228</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7226</v>
+        <v>1.1091</v>
       </c>
       <c r="L9" t="n">
-        <v>1.5692</v>
+        <v>-0.7863</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0152</v>
+        <v>0.0499</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.4331</v>
+        <v>-0.3684</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5821</v>
+        <v>0.4183</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2899</v>
+        <v>-0.0984</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4402</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7301</v>
+        <v>0.051</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3615</v>
+        <v>0.092</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1157</v>
+        <v>-0.3516</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4772</v>
+        <v>0.4436</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7524</v>
@@ -1234,13 +1234,13 @@
         <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9722</v>
+        <v>0.7027</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3462</v>
+        <v>0.1103</v>
       </c>
       <c r="U10" t="n">
-        <v>0.626</v>
+        <v>0.5924</v>
       </c>
       <c r="V10" t="n">
         <v>0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6704</v>
+        <v>-0.761</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2953</v>
+        <v>-0.5876</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3751</v>
+        <v>-0.1734</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3636</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6677</v>
+        <v>0.2416</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6642</v>
+        <v>0.0435</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0035</v>
+        <v>0.1981</v>
       </c>
       <c r="V11" t="n">
         <v>2.1444</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9982</v>
+        <v>-2.8974</v>
       </c>
       <c r="E12" t="n">
         <v>-2.865</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1332</v>
+        <v>-0.0324</v>
       </c>
       <c r="G12" t="n">
         <v>-1.831</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0075</v>
+        <v>0.0934</v>
       </c>
       <c r="T12" t="n">
         <v>-0.1494</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1419</v>
+        <v>0.2427</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>31.2956</v>
+        <v>31.29569999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>18.77869999999999</v>
+        <v>18.7787</v>
       </c>
       <c r="F13" t="n">
         <v>12.5168</v>
@@ -1441,13 +1441,13 @@
         <v>4.4506</v>
       </c>
       <c r="J13" t="n">
-        <v>21.0572</v>
+        <v>21.05719999999999</v>
       </c>
       <c r="K13" t="n">
         <v>15.7714</v>
       </c>
       <c r="L13" t="n">
-        <v>5.2859</v>
+        <v>5.285899999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-3.593900000000001</v>
@@ -1456,7 +1456,7 @@
         <v>-2.7583</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8353999999999998</v>
+        <v>-0.8353999999999999</v>
       </c>
       <c r="P13" t="n">
         <v>1.159800000000001</v>
@@ -1468,10 +1468,10 @@
         <v>15.0769</v>
       </c>
       <c r="S13" t="n">
-        <v>5.561599999999999</v>
+        <v>5.5616</v>
       </c>
       <c r="T13" t="n">
-        <v>2.635699999999999</v>
+        <v>2.6356</v>
       </c>
       <c r="U13" t="n">
         <v>2.9257</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5381</v>
+        <v>2.6617</v>
       </c>
       <c r="E14" t="n">
-        <v>3.012</v>
+        <v>2.0684</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5262</v>
+        <v>0.5934</v>
       </c>
       <c r="G14" t="n">
         <v>1.4513</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0868</v>
+        <v>0.2104</v>
       </c>
       <c r="T14" t="n">
-        <v>0.9831</v>
+        <v>0.0395</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1037</v>
+        <v>0.1709</v>
       </c>
       <c r="V14" t="n">
         <v>0.5361</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.8813</v>
+        <v>-1.128</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3627</v>
+        <v>0.1268</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.244</v>
+        <v>-1.2548</v>
       </c>
       <c r="G15" t="n">
         <v>0.6763</v>
@@ -1624,13 +1624,13 @@
         <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2535</v>
+        <v>-0.5001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1019</v>
+        <v>-0.3378</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1516</v>
+        <v>-0.1623</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>S. DINWIDDIE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2871</v>
+        <v>-1.1604</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6573</v>
+        <v>0.3913</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9444</v>
+        <v>-1.5517</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.295</v>
+        <v>1.9705</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3481</v>
+        <v>1.0035</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9469</v>
+        <v>0.967</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0203</v>
+        <v>3.7509</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0203</v>
+        <v>2.2554</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.4956</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.3153</v>
+        <v>-1.7804</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3684</v>
+        <v>-1.2518</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9469</v>
+        <v>-0.5286</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.5975</v>
       </c>
       <c r="T16" t="n">
-        <v>0.637</v>
+        <v>-0.4165</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6291</v>
+        <v>-0.181</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7326</v>
+        <v>-1.4837</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7719</v>
+        <v>0.3034</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.5046</v>
+        <v>-1.7871</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6245000000000001</v>
+        <v>-1.295</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9915</v>
+        <v>-0.3481</v>
       </c>
       <c r="I17" t="n">
-        <v>1.616</v>
+        <v>-0.9469</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4792</v>
+        <v>0.0203</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0707</v>
+        <v>0.0203</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4085</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8547</v>
+        <v>-1.3153</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0622</v>
+        <v>-0.3684</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2075</v>
+        <v>-0.9469</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5553</v>
+        <v>-0.1887</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6844</v>
+        <v>0.2831</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1291</v>
+        <v>-0.4718</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.6805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0394</v>
+        <v>-2.3539</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.405</v>
+        <v>-0.8768</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6344</v>
+        <v>-1.4772</v>
       </c>
       <c r="G19" t="n">
         <v>-4.4063</v>
@@ -1936,13 +1936,13 @@
         <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2794</v>
+        <v>-0.0351</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3189</v>
+        <v>-0.1529</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0395</v>
+        <v>0.1177</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. DINWIDDIE</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0583</v>
+        <v>-2.4039</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0805</v>
+        <v>-1.842</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9778</v>
+        <v>-0.5618</v>
       </c>
       <c r="G20" t="n">
-        <v>1.9705</v>
+        <v>-0.3816</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0035</v>
+        <v>-0.6627</v>
       </c>
       <c r="I20" t="n">
-        <v>0.967</v>
+        <v>0.2811</v>
       </c>
       <c r="J20" t="n">
-        <v>3.7509</v>
+        <v>0.9881</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2554</v>
+        <v>0.9144</v>
       </c>
       <c r="L20" t="n">
-        <v>1.4956</v>
+        <v>0.0736</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7804</v>
+        <v>-1.3696</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2518</v>
+        <v>-1.5771</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5286</v>
+        <v>0.2075</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4954</v>
+        <v>-0.396</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8883</v>
+        <v>-0.6524</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6071</v>
+        <v>0.2563</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.9304</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5618</v>
+        <v>-2.4175</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0779</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4838</v>
+        <v>-2.4817</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3816</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6627</v>
+        <v>-0.9915</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2811</v>
+        <v>1.616</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9881</v>
+        <v>1.4792</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9144</v>
+        <v>0.0707</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>1.4085</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3696</v>
+        <v>-0.8547</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5771</v>
+        <v>-1.0622</v>
       </c>
       <c r="O21" t="n">
         <v>0.2075</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.554</v>
+        <v>-0.1296</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8883</v>
+        <v>-0.0233</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3343</v>
+        <v>-0.1063</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9304</v>
+        <v>-2.6805</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.7979</v>
+        <v>-3.5284</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9624</v>
+        <v>-1.7265</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8355</v>
+        <v>-1.8019</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4677</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8817</v>
+        <v>-0.6122</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8057</v>
+        <v>-0.5698</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6083</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0832</v>
+        <v>-3.5475</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0313</v>
+        <v>-1.3912</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0519</v>
+        <v>-2.1563</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.0139</v>
+        <v>-3.1149</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3613</v>
+        <v>-2.0743</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6526</v>
+        <v>-1.0406</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9189</v>
+        <v>-0.9668</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.9522</v>
+        <v>-1.5055</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0333</v>
+        <v>0.5386</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0949</v>
+        <v>-2.1481</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4091</v>
+        <v>-0.5688</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6859</v>
+        <v>-1.5792</v>
       </c>
       <c r="P23" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.232</v>
       </c>
       <c r="R23" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3888</v>
+        <v>-0.7547</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8804</v>
+        <v>-0.1924</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4916</v>
+        <v>-0.5623</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.311</v>
+        <v>-3.6893</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.863</v>
+        <v>-2.5594</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.448</v>
+        <v>-1.1299</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.1149</v>
+        <v>-4.0139</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.0743</v>
+        <v>-3.3613</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.0406</v>
+        <v>-0.6526</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.9668</v>
+        <v>-1.9189</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5055</v>
+        <v>-1.9522</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5386</v>
+        <v>0.0333</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.1481</v>
+        <v>-2.0949</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.5688</v>
+        <v>-1.4091</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.5792</v>
+        <v>-0.6859</v>
       </c>
       <c r="P24" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="Q24" t="n">
         <v>-0.232</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5182</v>
+        <v>0.005</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6642</v>
+        <v>-0.4086</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.854</v>
+        <v>0.4136</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.0619</v>
+        <v>-8.652900000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2495</v>
+        <v>-5.4239</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.8124</v>
+        <v>-3.229</v>
       </c>
       <c r="G25" t="n">
         <v>-5.6392</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.4074</v>
+        <v>-0.9983</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3285</v>
+        <v>-0.5028</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0789</v>
+        <v>-0.4955</v>
       </c>
       <c r="V25" t="n">
         <v>0.5361</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-31.2956</v>
+        <v>-29.723</v>
       </c>
       <c r="E26" t="n">
         <v>-11.9807</v>
       </c>
       <c r="F26" t="n">
-        <v>-19.3147</v>
+        <v>-17.7421</v>
       </c>
       <c r="G26" t="n">
         <v>-17.4633</v>
@@ -2461,7 +2461,7 @@
         <v>2.758499999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8355000000000001</v>
+        <v>0.8355000000000006</v>
       </c>
       <c r="M26" t="n">
         <v>-21.0571</v>
@@ -2482,13 +2482,13 @@
         <v>13.9175</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.5617</v>
+        <v>-3.9889</v>
       </c>
       <c r="T26" t="n">
         <v>-2.926</v>
       </c>
       <c r="U26" t="n">
-        <v>-2.6357</v>
+        <v>-1.0631</v>
       </c>
       <c r="V26" t="n">
         <v>-7.1111</v>
